--- a/palmjobs_tracker.xlsx
+++ b/palmjobs_tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,6 +586,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:23:29 UTC</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/palmjobs_tracker.xlsx
+++ b/palmjobs_tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,6 +599,19 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:38:29 UTC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/palmjobs_tracker.xlsx
+++ b/palmjobs_tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,6 +612,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:59:55 UTC</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/palmjobs_tracker.xlsx
+++ b/palmjobs_tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,6 +625,19 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:21 UTC</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
         <v>0</v>
       </c>
     </row>

--- a/palmjobs_tracker.xlsx
+++ b/palmjobs_tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,6 +638,19 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:51:01 UTC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/palmjobs_tracker.xlsx
+++ b/palmjobs_tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,6 +651,19 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:06:43 UTC</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
         <v>0</v>
       </c>
     </row>

--- a/palmjobs_tracker.xlsx
+++ b/palmjobs_tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,6 +664,19 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:16:29 UTC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
         <v>0</v>
       </c>
     </row>
